--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/60.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/60.xlsx
@@ -426,13 +426,13 @@
         <v>-6.73281034680882</v>
       </c>
       <c r="E2">
-        <v>-7.994529333582782</v>
+        <v>-8.411357252092808</v>
       </c>
       <c r="F2">
-        <v>0.007664736330596073</v>
+        <v>0.7286492159703962</v>
       </c>
       <c r="G2">
-        <v>-5.351100324319904</v>
+        <v>-6.711714624710166</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.681584145030725</v>
       </c>
       <c r="E3">
-        <v>-7.451846065451582</v>
+        <v>-8.18679928300045</v>
       </c>
       <c r="F3">
-        <v>0.341240005763929</v>
+        <v>0.6948476840991623</v>
       </c>
       <c r="G3">
-        <v>-6.373469900254808</v>
+        <v>-7.320302474669734</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.581474555540899</v>
       </c>
       <c r="E4">
-        <v>-8.332389722347052</v>
+        <v>-9.259010602270568</v>
       </c>
       <c r="F4">
-        <v>0.3186653373028369</v>
+        <v>1.015154992841856</v>
       </c>
       <c r="G4">
-        <v>-6.741675458769455</v>
+        <v>-7.608692318750889</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.442538620165471</v>
       </c>
       <c r="E5">
-        <v>-10.02332191681116</v>
+        <v>-9.503090822809993</v>
       </c>
       <c r="F5">
-        <v>0.5414564070205695</v>
+        <v>0.4285441314471773</v>
       </c>
       <c r="G5">
-        <v>-5.892403444981499</v>
+        <v>-7.049667320446733</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.275965601600646</v>
       </c>
       <c r="E6">
-        <v>-10.30156041679045</v>
+        <v>-9.297665656400042</v>
       </c>
       <c r="F6">
-        <v>0.5704674902014137</v>
+        <v>0.9846810128276674</v>
       </c>
       <c r="G6">
-        <v>-6.456471680822521</v>
+        <v>-6.515159609634749</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.094931947608968</v>
       </c>
       <c r="E7">
-        <v>-10.46263823724328</v>
+        <v>-9.831486700898232</v>
       </c>
       <c r="F7">
-        <v>0.6112463607064278</v>
+        <v>1.860566883321364</v>
       </c>
       <c r="G7">
-        <v>-6.79453921931367</v>
+        <v>-5.885785221096099</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.917928700021269</v>
       </c>
       <c r="E8">
-        <v>-11.54188227664731</v>
+        <v>-10.77772493022298</v>
       </c>
       <c r="F8">
-        <v>0.9080851925604083</v>
+        <v>1.481484422247837</v>
       </c>
       <c r="G8">
-        <v>-5.686916944821274</v>
+        <v>-6.836079484256239</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.761361253364179</v>
       </c>
       <c r="E9">
-        <v>-13.07134720189393</v>
+        <v>-13.41953703986969</v>
       </c>
       <c r="F9">
-        <v>0.5514962199424995</v>
+        <v>1.399146359144372</v>
       </c>
       <c r="G9">
-        <v>-5.623937178209292</v>
+        <v>-5.318888572270835</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.637782720182165</v>
       </c>
       <c r="E10">
-        <v>-12.55750125624357</v>
+        <v>-13.28297637769439</v>
       </c>
       <c r="F10">
-        <v>0.7652763090525792</v>
+        <v>1.911372312869863</v>
       </c>
       <c r="G10">
-        <v>-4.780059492665062</v>
+        <v>-6.149293562091985</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.554765451764021</v>
       </c>
       <c r="E11">
-        <v>-13.31143330835859</v>
+        <v>-13.29252692937656</v>
       </c>
       <c r="F11">
-        <v>0.588488623049317</v>
+        <v>2.120773651888745</v>
       </c>
       <c r="G11">
-        <v>-4.288863906437747</v>
+        <v>-6.863658151463373</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.521606885920284</v>
       </c>
       <c r="E12">
-        <v>-14.66160236221951</v>
+        <v>-15.68480200730461</v>
       </c>
       <c r="F12">
-        <v>0.5262765743642686</v>
+        <v>1.783992600606578</v>
       </c>
       <c r="G12">
-        <v>-4.098123215965667</v>
+        <v>-5.877322950694291</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.54008372851602</v>
       </c>
       <c r="E13">
-        <v>-16.0248541774886</v>
+        <v>-16.38109564225</v>
       </c>
       <c r="F13">
-        <v>1.23441059048444</v>
+        <v>1.842916030702512</v>
       </c>
       <c r="G13">
-        <v>-4.245879904009022</v>
+        <v>-3.655174711548427</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.614848477515389</v>
       </c>
       <c r="E14">
-        <v>-16.79127123244276</v>
+        <v>-17.52176390309407</v>
       </c>
       <c r="F14">
-        <v>1.022973124389477</v>
+        <v>1.758063044164147</v>
       </c>
       <c r="G14">
-        <v>-3.31183753123281</v>
+        <v>-3.10478260716717</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.743515858925287</v>
       </c>
       <c r="E15">
-        <v>-16.25213828793357</v>
+        <v>-19.10174395589625</v>
       </c>
       <c r="F15">
-        <v>1.472455217557323</v>
+        <v>2.292209256102519</v>
       </c>
       <c r="G15">
-        <v>-3.557870086203094</v>
+        <v>-2.476851956114676</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.919281462309189</v>
       </c>
       <c r="E16">
-        <v>-18.41354270400257</v>
+        <v>-18.04005681021996</v>
       </c>
       <c r="F16">
-        <v>1.242659473081517</v>
+        <v>2.107673849780873</v>
       </c>
       <c r="G16">
-        <v>-2.999416020450282</v>
+        <v>-3.526216141819131</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.1307131225075</v>
       </c>
       <c r="E17">
-        <v>-17.82758533825407</v>
+        <v>-19.30625437055665</v>
       </c>
       <c r="F17">
-        <v>1.109449711037329</v>
+        <v>2.185265367666297</v>
       </c>
       <c r="G17">
-        <v>-2.635187302465681</v>
+        <v>-2.783580547491568</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.371141106359735</v>
       </c>
       <c r="E18">
-        <v>-20.1880207154342</v>
+        <v>-19.41334372389004</v>
       </c>
       <c r="F18">
-        <v>1.897621413983391</v>
+        <v>3.18124628748306</v>
       </c>
       <c r="G18">
-        <v>-1.958163014440774</v>
+        <v>-2.495522106787916</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.630044157203899</v>
       </c>
       <c r="E19">
-        <v>-20.1368987723616</v>
+        <v>-19.08924083916108</v>
       </c>
       <c r="F19">
-        <v>1.764194619679669</v>
+        <v>2.55844653936228</v>
       </c>
       <c r="G19">
-        <v>-1.600972516701182</v>
+        <v>-2.992213739127301</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.902739785517368</v>
       </c>
       <c r="E20">
-        <v>-21.31956410115281</v>
+        <v>-21.03484988334256</v>
       </c>
       <c r="F20">
-        <v>1.957017013498922</v>
+        <v>2.943925653520224</v>
       </c>
       <c r="G20">
-        <v>-0.9550870212754056</v>
+        <v>-1.371319819755646</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.182921089955557</v>
       </c>
       <c r="E21">
-        <v>-20.32773319551884</v>
+        <v>-23.12652485664145</v>
       </c>
       <c r="F21">
-        <v>2.056131173243883</v>
+        <v>3.818688257815725</v>
       </c>
       <c r="G21">
-        <v>-1.838795455329735</v>
+        <v>-1.206143126453199</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.464322304629126</v>
       </c>
       <c r="E22">
-        <v>-22.13924506738519</v>
+        <v>-22.46961536014077</v>
       </c>
       <c r="F22">
-        <v>2.256412187157941</v>
+        <v>2.713510290227125</v>
       </c>
       <c r="G22">
-        <v>-0.5604052859975979</v>
+        <v>-0.493507740843639</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.74061757061902</v>
       </c>
       <c r="E23">
-        <v>-23.06271412939937</v>
+        <v>-23.29167830370119</v>
       </c>
       <c r="F23">
-        <v>1.886884115708304</v>
+        <v>3.49525883233188</v>
       </c>
       <c r="G23">
-        <v>-0.06483911265310303</v>
+        <v>-2.664413142895655</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.013470142002923</v>
       </c>
       <c r="E24">
-        <v>-23.31653509752929</v>
+        <v>-23.41345802671546</v>
       </c>
       <c r="F24">
-        <v>2.404660131032552</v>
+        <v>3.499998750610699</v>
       </c>
       <c r="G24">
-        <v>-0.9717884390129792</v>
+        <v>-1.03843989254998</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.282331310508047</v>
       </c>
       <c r="E25">
-        <v>-23.16737169219064</v>
+        <v>-23.20514369388862</v>
       </c>
       <c r="F25">
-        <v>2.460707469505966</v>
+        <v>3.796890597978459</v>
       </c>
       <c r="G25">
-        <v>0.1011414799314079</v>
+        <v>-1.006779385722897</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.551366600811447</v>
       </c>
       <c r="E26">
-        <v>-23.77190032984459</v>
+        <v>-24.50734715106029</v>
       </c>
       <c r="F26">
-        <v>1.974778867349748</v>
+        <v>3.987703372478519</v>
       </c>
       <c r="G26">
-        <v>-0.4280834641698709</v>
+        <v>0.348217463357595</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.821751742697293</v>
       </c>
       <c r="E27">
-        <v>-23.06510969214942</v>
+        <v>-23.59196141514981</v>
       </c>
       <c r="F27">
-        <v>2.345895747477955</v>
+        <v>4.450091429781981</v>
       </c>
       <c r="G27">
-        <v>-0.2401219683586397</v>
+        <v>-0.9168279778922801</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.091710912384467</v>
       </c>
       <c r="E28">
-        <v>-23.7981790645111</v>
+        <v>-24.19173968356972</v>
       </c>
       <c r="F28">
-        <v>2.176299118898395</v>
+        <v>3.751471213282962</v>
       </c>
       <c r="G28">
-        <v>0.5233165706558028</v>
+        <v>-0.4090884725622454</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.357260376207137</v>
       </c>
       <c r="E29">
-        <v>-22.84258953636052</v>
+        <v>-24.37500702666014</v>
       </c>
       <c r="F29">
-        <v>2.391727659140046</v>
+        <v>4.214193931017154</v>
       </c>
       <c r="G29">
-        <v>0.532297274064003</v>
+        <v>-0.3898145771220671</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.619147600189187</v>
       </c>
       <c r="E30">
-        <v>-21.88009408534824</v>
+        <v>-23.1969290420387</v>
       </c>
       <c r="F30">
-        <v>2.56836209717379</v>
+        <v>3.963599537791859</v>
       </c>
       <c r="G30">
-        <v>-0.4123040696905012</v>
+        <v>-0.329400725769571</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.873602081166425</v>
       </c>
       <c r="E31">
-        <v>-23.08952269552477</v>
+        <v>-23.0731839613051</v>
       </c>
       <c r="F31">
-        <v>2.615358693404217</v>
+        <v>2.956256730678298</v>
       </c>
       <c r="G31">
-        <v>0.5291932384687683</v>
+        <v>-0.9275936658288183</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.12016954847005</v>
       </c>
       <c r="E32">
-        <v>-23.02197597722637</v>
+        <v>-21.95273533690528</v>
       </c>
       <c r="F32">
-        <v>2.303950535669799</v>
+        <v>3.631377820694701</v>
       </c>
       <c r="G32">
-        <v>-0.245480203165213</v>
+        <v>-0.3455180860695635</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.35422241305657</v>
       </c>
       <c r="E33">
-        <v>-22.36408380186602</v>
+        <v>-21.704017958982</v>
       </c>
       <c r="F33">
-        <v>2.523789303963954</v>
+        <v>4.012504692518337</v>
       </c>
       <c r="G33">
-        <v>-1.014756035333908</v>
+        <v>-0.0404891674604638</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.56748640464444</v>
       </c>
       <c r="E34">
-        <v>-21.42826559123293</v>
+        <v>-21.62343829248951</v>
       </c>
       <c r="F34">
-        <v>2.139628950711267</v>
+        <v>3.260517734461362</v>
       </c>
       <c r="G34">
-        <v>-0.9112695885705808</v>
+        <v>-1.380910830373903</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.75100092442161</v>
       </c>
       <c r="E35">
-        <v>-20.4640900763638</v>
+        <v>-22.26380527344017</v>
       </c>
       <c r="F35">
-        <v>2.400387411968912</v>
+        <v>4.23611584596484</v>
       </c>
       <c r="G35">
-        <v>-1.637613917855501</v>
+        <v>-2.611470633034014</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.9000221165487</v>
       </c>
       <c r="E36">
-        <v>-19.72526048506437</v>
+        <v>-21.9946056075802</v>
       </c>
       <c r="F36">
-        <v>2.075054398193434</v>
+        <v>3.282297170215767</v>
       </c>
       <c r="G36">
-        <v>-1.390518247099957</v>
+        <v>-2.874181637190955</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.00807537852766</v>
       </c>
       <c r="E37">
-        <v>-19.75053842697518</v>
+        <v>-21.29470730732471</v>
       </c>
       <c r="F37">
-        <v>2.612996189571433</v>
+        <v>4.158734733399728</v>
       </c>
       <c r="G37">
-        <v>-1.517120899749572</v>
+        <v>-1.30422868252968</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.07476541516462</v>
       </c>
       <c r="E38">
-        <v>-19.02855475898428</v>
+        <v>-19.78722359491132</v>
       </c>
       <c r="F38">
-        <v>2.587149469869283</v>
+        <v>3.398667879695846</v>
       </c>
       <c r="G38">
-        <v>-2.814033564784774</v>
+        <v>-2.924417139266054</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.09811709821899</v>
       </c>
       <c r="E39">
-        <v>-19.6283964260403</v>
+        <v>-20.11583683975193</v>
       </c>
       <c r="F39">
-        <v>2.816396835124435</v>
+        <v>4.380866422664831</v>
       </c>
       <c r="G39">
-        <v>-3.083539978791325</v>
+        <v>-3.735630264186012</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.07594650264834</v>
       </c>
       <c r="E40">
-        <v>-16.8777288581972</v>
+        <v>-19.24503393044696</v>
       </c>
       <c r="F40">
-        <v>2.695899199243608</v>
+        <v>3.973294749874225</v>
       </c>
       <c r="G40">
-        <v>-2.785267095373122</v>
+        <v>-3.433721787279944</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.0094033281191</v>
       </c>
       <c r="E41">
-        <v>-17.8973827081343</v>
+        <v>-18.86370471968306</v>
       </c>
       <c r="F41">
-        <v>2.973708775120478</v>
+        <v>4.363480647614876</v>
       </c>
       <c r="G41">
-        <v>-4.271214215669494</v>
+        <v>-2.884149988288548</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.90443959625871</v>
       </c>
       <c r="E42">
-        <v>-16.38260815256856</v>
+        <v>-18.11114026671836</v>
       </c>
       <c r="F42">
-        <v>2.779738264080946</v>
+        <v>3.851307709403164</v>
       </c>
       <c r="G42">
-        <v>-3.831025218583748</v>
+        <v>-3.68298962670784</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.7673519811689</v>
       </c>
       <c r="E43">
-        <v>-15.27473057201403</v>
+        <v>-17.24715723926894</v>
       </c>
       <c r="F43">
-        <v>2.970746533288067</v>
+        <v>3.820904968985616</v>
       </c>
       <c r="G43">
-        <v>-4.091386868104126</v>
+        <v>-4.206928522876853</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.6096810646912</v>
       </c>
       <c r="E44">
-        <v>-15.23509283902489</v>
+        <v>-18.37680319437834</v>
       </c>
       <c r="F44">
-        <v>3.181607455670681</v>
+        <v>3.871851220992591</v>
       </c>
       <c r="G44">
-        <v>-4.097384941114791</v>
+        <v>-4.415535464740111</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.43936414544097</v>
       </c>
       <c r="E45">
-        <v>-14.4981153935946</v>
+        <v>-17.28613381505296</v>
       </c>
       <c r="F45">
-        <v>3.43636025325803</v>
+        <v>3.616601402963563</v>
       </c>
       <c r="G45">
-        <v>-4.307025467769273</v>
+        <v>-5.357629955223199</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.261426424487</v>
       </c>
       <c r="E46">
-        <v>-14.96637319140974</v>
+        <v>-12.8791587650084</v>
       </c>
       <c r="F46">
-        <v>3.771072042768004</v>
+        <v>4.540520985675991</v>
       </c>
       <c r="G46">
-        <v>-4.285884557261771</v>
+        <v>-5.479271400874933</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.08220676429772</v>
       </c>
       <c r="E47">
-        <v>-13.55169602530955</v>
+        <v>-14.43147889857173</v>
       </c>
       <c r="F47">
-        <v>3.11943019841655</v>
+        <v>3.7107967170707</v>
       </c>
       <c r="G47">
-        <v>-3.527761597173629</v>
+        <v>-3.92804109643185</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.908934376184263</v>
       </c>
       <c r="E48">
-        <v>-12.00795282151674</v>
+        <v>-12.87031012679741</v>
       </c>
       <c r="F48">
-        <v>3.649466051302231</v>
+        <v>4.2438859322031</v>
       </c>
       <c r="G48">
-        <v>-5.060554717674194</v>
+        <v>-3.456017687776371</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.747770192755093</v>
       </c>
       <c r="E49">
-        <v>-12.64457928293707</v>
+        <v>-11.9569169194503</v>
       </c>
       <c r="F49">
-        <v>3.088512213474461</v>
+        <v>3.655539641099557</v>
       </c>
       <c r="G49">
-        <v>-4.734322545347962</v>
+        <v>-5.036175241487519</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.606731283568413</v>
       </c>
       <c r="E50">
-        <v>-11.1192171551414</v>
+        <v>-13.11615645219983</v>
       </c>
       <c r="F50">
-        <v>3.488487757181397</v>
+        <v>4.236813331317998</v>
       </c>
       <c r="G50">
-        <v>-4.637513384458105</v>
+        <v>-4.55558128211877</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.487530758253344</v>
       </c>
       <c r="E51">
-        <v>-9.184711929226721</v>
+        <v>-11.93168426227956</v>
       </c>
       <c r="F51">
-        <v>3.465908118515888</v>
+        <v>4.106796097244199</v>
       </c>
       <c r="G51">
-        <v>-5.149669414007152</v>
+        <v>-5.756879150911754</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.386526733814778</v>
       </c>
       <c r="E52">
-        <v>-9.466745290424431</v>
+        <v>-10.9397401447954</v>
       </c>
       <c r="F52">
-        <v>3.751640200233133</v>
+        <v>4.19502716605118</v>
       </c>
       <c r="G52">
-        <v>-4.662969101316278</v>
+        <v>-4.358363460288346</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.300187145098089</v>
       </c>
       <c r="E53">
-        <v>-8.874882794569929</v>
+        <v>-8.265051313852993</v>
       </c>
       <c r="F53">
-        <v>3.437355950876195</v>
+        <v>3.944510639361747</v>
       </c>
       <c r="G53">
-        <v>-4.86545328374961</v>
+        <v>-5.182137101337858</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.223587265735656</v>
       </c>
       <c r="E54">
-        <v>-8.028080797505611</v>
+        <v>-8.666482420736941</v>
       </c>
       <c r="F54">
-        <v>3.413392938648011</v>
+        <v>4.466458312926493</v>
       </c>
       <c r="G54">
-        <v>-5.408839980101453</v>
+        <v>-5.365193170917719</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.151753074587674</v>
       </c>
       <c r="E55">
-        <v>-7.491972873633549</v>
+        <v>-7.494083142521123</v>
       </c>
       <c r="F55">
-        <v>3.259116136815825</v>
+        <v>3.984379962458488</v>
       </c>
       <c r="G55">
-        <v>-4.839702256951089</v>
+        <v>-5.110261943078221</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.081566286586158</v>
       </c>
       <c r="E56">
-        <v>-7.108139416743409</v>
+        <v>-8.944557895651947</v>
       </c>
       <c r="F56">
-        <v>3.23411435186453</v>
+        <v>3.381419613634755</v>
       </c>
       <c r="G56">
-        <v>-5.486956021767153</v>
+        <v>-6.230146142538262</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.006231245791311</v>
       </c>
       <c r="E57">
-        <v>-5.603757709025278</v>
+        <v>-8.126163016037744</v>
       </c>
       <c r="F57">
-        <v>3.321149258141869</v>
+        <v>3.784519759185051</v>
       </c>
       <c r="G57">
-        <v>-5.922321623160515</v>
+        <v>-6.099701179442538</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.916904527965931</v>
       </c>
       <c r="E58">
-        <v>-5.662129738984149</v>
+        <v>-6.516344847999024</v>
       </c>
       <c r="F58">
-        <v>2.806206259335196</v>
+        <v>3.92445255107036</v>
       </c>
       <c r="G58">
-        <v>-4.904644194055618</v>
+        <v>-5.685994921563069</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.808499683753386</v>
       </c>
       <c r="E59">
-        <v>-6.753102526068045</v>
+        <v>-7.294205356770568</v>
       </c>
       <c r="F59">
-        <v>3.06025660136497</v>
+        <v>3.745612999010364</v>
       </c>
       <c r="G59">
-        <v>-6.097647134746325</v>
+        <v>-5.122208870776159</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.676753951986788</v>
       </c>
       <c r="E60">
-        <v>-5.932022261367295</v>
+        <v>-5.878423243012509</v>
       </c>
       <c r="F60">
-        <v>2.486781161876484</v>
+        <v>3.373013341231146</v>
       </c>
       <c r="G60">
-        <v>-6.288578136068853</v>
+        <v>-5.180909924474626</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.521220411324252</v>
       </c>
       <c r="E61">
-        <v>-4.170703995401963</v>
+        <v>-4.591408287662555</v>
       </c>
       <c r="F61">
-        <v>2.615925296707732</v>
+        <v>3.492086185179158</v>
       </c>
       <c r="G61">
-        <v>-5.633383815078933</v>
+        <v>-6.250844088135239</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.344392902202211</v>
       </c>
       <c r="E62">
-        <v>-3.700304229381197</v>
+        <v>-5.052850732096148</v>
       </c>
       <c r="F62">
-        <v>2.805382862136813</v>
+        <v>3.627792646575384</v>
       </c>
       <c r="G62">
-        <v>-5.45571223007812</v>
+        <v>-5.833754890827984</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.147051341138836</v>
       </c>
       <c r="E63">
-        <v>-4.542573223963838</v>
+        <v>-4.636149610858338</v>
       </c>
       <c r="F63">
-        <v>3.115553438971448</v>
+        <v>3.938027836067438</v>
       </c>
       <c r="G63">
-        <v>-5.541293050791557</v>
+        <v>-6.467056901573289</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.92893555114552</v>
       </c>
       <c r="E64">
-        <v>-3.104148740167425</v>
+        <v>-3.925265232660237</v>
       </c>
       <c r="F64">
-        <v>2.601672407175164</v>
+        <v>3.745419161038109</v>
       </c>
       <c r="G64">
-        <v>-4.921578578523913</v>
+        <v>-5.706696148381607</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.693173671087395</v>
       </c>
       <c r="E65">
-        <v>-2.90120064903967</v>
+        <v>-6.051886439876322</v>
       </c>
       <c r="F65">
-        <v>2.680557834943761</v>
+        <v>3.806817752933608</v>
       </c>
       <c r="G65">
-        <v>-5.706525524860515</v>
+        <v>-5.572868245858094</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.442314056800875</v>
       </c>
       <c r="E66">
-        <v>-1.930078455042777</v>
+        <v>-3.640274777935518</v>
       </c>
       <c r="F66">
-        <v>2.56450356181155</v>
+        <v>3.186561092739422</v>
       </c>
       <c r="G66">
-        <v>-4.816241522801058</v>
+        <v>-5.616252557317072</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.182088995508782</v>
       </c>
       <c r="E67">
-        <v>-2.43421082394668</v>
+        <v>-4.854014495367358</v>
       </c>
       <c r="F67">
-        <v>2.491342152796298</v>
+        <v>3.280045667614957</v>
       </c>
       <c r="G67">
-        <v>-5.590760747021746</v>
+        <v>-5.870465197635052</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.919161715764588</v>
       </c>
       <c r="E68">
-        <v>-2.633441037914137</v>
+        <v>-4.542011693186886</v>
       </c>
       <c r="F68">
-        <v>2.316008251584949</v>
+        <v>3.305826117924884</v>
       </c>
       <c r="G68">
-        <v>-5.030951536764883</v>
+        <v>-5.395469002246715</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.657624259541434</v>
       </c>
       <c r="E69">
-        <v>-2.927950345002979</v>
+        <v>-4.127121961552144</v>
       </c>
       <c r="F69">
-        <v>2.42330999473918</v>
+        <v>3.07347734511365</v>
       </c>
       <c r="G69">
-        <v>-4.643340833947679</v>
+        <v>-5.399485217435476</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.39930906798823</v>
       </c>
       <c r="E70">
-        <v>-3.110696913582516</v>
+        <v>-3.14188904254735</v>
       </c>
       <c r="F70">
-        <v>2.392867492686298</v>
+        <v>3.335832898723893</v>
       </c>
       <c r="G70">
-        <v>-4.650756394672024</v>
+        <v>-4.239871987333678</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.148295614978511</v>
       </c>
       <c r="E71">
-        <v>-2.721809679699817</v>
+        <v>-3.510438899661602</v>
       </c>
       <c r="F71">
-        <v>1.847124137108733</v>
+        <v>3.358498687599293</v>
       </c>
       <c r="G71">
-        <v>-3.438187529822348</v>
+        <v>-4.589971765283311</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.90701542791526</v>
       </c>
       <c r="E72">
-        <v>-2.164010365331013</v>
+        <v>-3.484309604637344</v>
       </c>
       <c r="F72">
-        <v>1.844644005104752</v>
+        <v>3.209129134261292</v>
       </c>
       <c r="G72">
-        <v>-3.822720446816793</v>
+        <v>-5.435785371547612</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.681475141089869</v>
       </c>
       <c r="E73">
-        <v>-3.887909850570964</v>
+        <v>-3.744615347546251</v>
       </c>
       <c r="F73">
-        <v>2.178905162747603</v>
+        <v>3.238208143569166</v>
       </c>
       <c r="G73">
-        <v>-2.967007395107646</v>
+        <v>-4.473258714413862</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.47742665558813</v>
       </c>
       <c r="E74">
-        <v>-2.11436923325893</v>
+        <v>-3.567158036607673</v>
       </c>
       <c r="F74">
-        <v>1.969058162066015</v>
+        <v>3.054030591965529</v>
       </c>
       <c r="G74">
-        <v>-2.781116350100425</v>
+        <v>-4.813862637170462</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.298616687135969</v>
       </c>
       <c r="E75">
-        <v>-2.204612663283785</v>
+        <v>-4.663564992500774</v>
       </c>
       <c r="F75">
-        <v>1.629049791382541</v>
+        <v>2.206580917675134</v>
       </c>
       <c r="G75">
-        <v>-2.812511077981192</v>
+        <v>-4.875447884619679</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.146242337699237</v>
       </c>
       <c r="E76">
-        <v>-2.273522452258505</v>
+        <v>-3.169394993669939</v>
       </c>
       <c r="F76">
-        <v>1.271599316665721</v>
+        <v>3.215234202019924</v>
       </c>
       <c r="G76">
-        <v>-3.099434216025275</v>
+        <v>-4.221257617426948</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.02483785075597</v>
       </c>
       <c r="E77">
-        <v>-3.914899555656679</v>
+        <v>-4.023039514959848</v>
       </c>
       <c r="F77">
-        <v>1.139171533449775</v>
+        <v>2.440364422828016</v>
       </c>
       <c r="G77">
-        <v>-3.060617364977045</v>
+        <v>-3.708140189960984</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.937181382004853</v>
       </c>
       <c r="E78">
-        <v>-3.81994198418984</v>
+        <v>-4.826938749275497</v>
       </c>
       <c r="F78">
-        <v>1.644787115300926</v>
+        <v>2.731741000027937</v>
       </c>
       <c r="G78">
-        <v>-3.363001619009232</v>
+        <v>-2.973727336861389</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.889356518889655</v>
       </c>
       <c r="E79">
-        <v>-4.448870039797122</v>
+        <v>-5.860042167015374</v>
       </c>
       <c r="F79">
-        <v>1.097559325337545</v>
+        <v>2.92907633945764</v>
       </c>
       <c r="G79">
-        <v>-0.6319982592031221</v>
+        <v>-3.673982673527164</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.886048716899552</v>
       </c>
       <c r="E80">
-        <v>-4.596249226376754</v>
+        <v>-6.554746307584068</v>
       </c>
       <c r="F80">
-        <v>1.174903989736935</v>
+        <v>2.135598114929245</v>
       </c>
       <c r="G80">
-        <v>-1.421899850094486</v>
+        <v>-2.468002501568853</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.929725617201938</v>
       </c>
       <c r="E81">
-        <v>-5.041891824997586</v>
+        <v>-6.307862961633896</v>
       </c>
       <c r="F81">
-        <v>0.8725565146543375</v>
+        <v>2.867419296932468</v>
       </c>
       <c r="G81">
-        <v>-0.176663143398979</v>
+        <v>-2.556273923961035</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.017959187181296</v>
       </c>
       <c r="E82">
-        <v>-6.372783165007858</v>
+        <v>-7.276938285379321</v>
       </c>
       <c r="F82">
-        <v>0.4256465022721846</v>
+        <v>2.22606743245859</v>
       </c>
       <c r="G82">
-        <v>-0.9507722149247357</v>
+        <v>-1.829571941526136</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.152726113510668</v>
       </c>
       <c r="E83">
-        <v>-6.438219614418695</v>
+        <v>-7.221505235051429</v>
       </c>
       <c r="F83">
-        <v>1.05370886850295</v>
+        <v>2.296036313503453</v>
       </c>
       <c r="G83">
-        <v>-0.1819163791156499</v>
+        <v>-3.431231340116325</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.332453679804989</v>
       </c>
       <c r="E84">
-        <v>-8.766529996988401</v>
+        <v>-9.637586500837802</v>
       </c>
       <c r="F84">
-        <v>0.9091703538580757</v>
+        <v>1.980917069804493</v>
       </c>
       <c r="G84">
-        <v>0.445433495720823</v>
+        <v>-2.174090361603152</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.557538784009481</v>
       </c>
       <c r="E85">
-        <v>-9.377633978901493</v>
+        <v>-8.432251631164199</v>
       </c>
       <c r="F85">
-        <v>0.5198633539317948</v>
+        <v>2.4757787860325</v>
       </c>
       <c r="G85">
-        <v>0.5142964925888893</v>
+        <v>-1.53828806002955</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.826281093962123</v>
       </c>
       <c r="E86">
-        <v>-10.1950869359221</v>
+        <v>-11.10086777846232</v>
       </c>
       <c r="F86">
-        <v>0.2284511569335539</v>
+        <v>0.9274176310069432</v>
       </c>
       <c r="G86">
-        <v>0.1254848626809283</v>
+        <v>-1.813129740291758</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.134667862706795</v>
       </c>
       <c r="E87">
-        <v>-11.30344000624743</v>
+        <v>-13.48740980829666</v>
       </c>
       <c r="F87">
-        <v>0.3056351180568007</v>
+        <v>2.296970711933811</v>
       </c>
       <c r="G87">
-        <v>0.3999032653619682</v>
+        <v>-1.35132405557239</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.472435919288388</v>
       </c>
       <c r="E88">
-        <v>-11.87002003171711</v>
+        <v>-13.41066575928867</v>
       </c>
       <c r="F88">
-        <v>0.2117206204992123</v>
+        <v>1.831125049091064</v>
       </c>
       <c r="G88">
-        <v>1.018085407161353</v>
+        <v>-2.332734142780745</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.836909985573943</v>
       </c>
       <c r="E89">
-        <v>-14.74805093102594</v>
+        <v>-14.49275368036951</v>
       </c>
       <c r="F89">
-        <v>-0.3182928664665926</v>
+        <v>0.9573316346568389</v>
       </c>
       <c r="G89">
-        <v>0.212420827898416</v>
+        <v>-0.829557328075729</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.221102038757754</v>
       </c>
       <c r="E90">
-        <v>-15.35055081232446</v>
+        <v>-18.4117267859255</v>
       </c>
       <c r="F90">
-        <v>-1.150172547053968</v>
+        <v>0.9032906020330047</v>
       </c>
       <c r="G90">
-        <v>0.3196970855629016</v>
+        <v>-1.65634969295993</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.620793430214674</v>
       </c>
       <c r="E91">
-        <v>-16.39648792540207</v>
+        <v>-18.15079611360353</v>
       </c>
       <c r="F91">
-        <v>-0.6124892063056426</v>
+        <v>0.9845302499603579</v>
       </c>
       <c r="G91">
-        <v>1.124246049495627</v>
+        <v>-0.6569322618333425</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.029848662200788</v>
       </c>
       <c r="E92">
-        <v>-20.31332811970044</v>
+        <v>-19.35793331593219</v>
       </c>
       <c r="F92">
-        <v>-0.7239402417804965</v>
+        <v>0.505674248689242</v>
       </c>
       <c r="G92">
-        <v>0.4555330956807939</v>
+        <v>-1.073542400792919</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.440732621131728</v>
       </c>
       <c r="E93">
-        <v>-21.47487264571987</v>
+        <v>-20.95837754277503</v>
       </c>
       <c r="F93">
-        <v>-1.248590878180577</v>
+        <v>0.7694678481107446</v>
       </c>
       <c r="G93">
-        <v>1.258103483013174</v>
+        <v>-2.410325188996934</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.839087939400219</v>
       </c>
       <c r="E94">
-        <v>-22.45373853026988</v>
+        <v>-24.55022274296492</v>
       </c>
       <c r="F94">
-        <v>-1.659076747494233</v>
+        <v>0.1127555668867554</v>
       </c>
       <c r="G94">
-        <v>0.4596182165223026</v>
+        <v>-2.043855396687232</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.220776517426684</v>
       </c>
       <c r="E95">
-        <v>-24.94197650089447</v>
+        <v>-25.86444024167895</v>
       </c>
       <c r="F95">
-        <v>-1.835600184296002</v>
+        <v>0.157614146850557</v>
       </c>
       <c r="G95">
-        <v>0.2318817529674826</v>
+        <v>-1.4169714553122</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.575481999639658</v>
       </c>
       <c r="E96">
-        <v>-27.41531126355982</v>
+        <v>-27.17472702495432</v>
       </c>
       <c r="F96">
-        <v>-1.850955630841697</v>
+        <v>0.003807029335758776</v>
       </c>
       <c r="G96">
-        <v>0.2800861788972849</v>
+        <v>-1.973496162788059</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.898321689053336</v>
       </c>
       <c r="E97">
-        <v>-28.49128574473032</v>
+        <v>-30.9247903142612</v>
       </c>
       <c r="F97">
-        <v>-2.010130569126636</v>
+        <v>-0.5533023553756179</v>
       </c>
       <c r="G97">
-        <v>-0.3908350370270544</v>
+        <v>-2.420916972190822</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.17957070018301</v>
       </c>
       <c r="E98">
-        <v>-31.50672186661688</v>
+        <v>-32.50866711894698</v>
       </c>
       <c r="F98">
-        <v>-2.124960515237509</v>
+        <v>-0.3279110403804977</v>
       </c>
       <c r="G98">
-        <v>-0.258119468612194</v>
+        <v>-3.293246129876997</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.4119227090554</v>
       </c>
       <c r="E99">
-        <v>-34.37405877455659</v>
+        <v>-34.74153085485702</v>
       </c>
       <c r="F99">
-        <v>-2.179546613612385</v>
+        <v>-0.2242980172709327</v>
       </c>
       <c r="G99">
-        <v>-0.6866174732816389</v>
+        <v>-2.730126167066654</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.57593307579736</v>
       </c>
       <c r="E100">
-        <v>-36.02036738614912</v>
+        <v>-37.5940279534736</v>
       </c>
       <c r="F100">
-        <v>-2.691028693410162</v>
+        <v>-0.5483023297323201</v>
       </c>
       <c r="G100">
-        <v>-1.930942000383621</v>
+        <v>-2.67236026151263</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.67231364633273</v>
       </c>
       <c r="E101">
-        <v>-38.29189523313665</v>
+        <v>-39.58108159177328</v>
       </c>
       <c r="F101">
-        <v>-2.996414620126228</v>
+        <v>-0.9366533936757704</v>
       </c>
       <c r="G101">
-        <v>-1.252139290273495</v>
+        <v>-3.151011737718187</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.67934811157239</v>
       </c>
       <c r="E102">
-        <v>-39.08599711393671</v>
+        <v>-42.74108018940671</v>
       </c>
       <c r="F102">
-        <v>-2.766125997045757</v>
+        <v>-1.309039332665066</v>
       </c>
       <c r="G102">
-        <v>-2.249305803410304</v>
+        <v>-2.634058562249232</v>
       </c>
     </row>
   </sheetData>
